--- a/docs/06-testing/dist/Test_Cases.xlsx
+++ b/docs/06-testing/dist/Test_Cases.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test cases'!$A$1:$K$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Truy vết'!$A$1:$E$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test cases'!$A$1:$K$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Truy vết'!$A$1:$E$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4540,22 +4540,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-RS.1</t>
+          <t>TC-AC-RG.2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Đổi lịch khám: AC-RS.1</t>
+          <t>Đăng ký tài khoản bệnh nhân: AC-RG.2</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>AC-RS.1</t>
+          <t>AC-RG.2</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>scheduling</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4581,29 +4581,29 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>qnt124</t>
+          <t>Her55chers</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Given slot mới vừa bị người khác đặt, When đổi lịch, Then lịch cũ vẫn “booked” và không có lịch hẹn mới.</t>
+          <t>Given số điện thoại chưa xác minh bằng mã OTP, When tạo hồ sơ, Then bị từ chối và không tạo hồ sơ.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-RS.2</t>
+          <t>TC-AC-RS.1</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Đổi lịch khám: AC-RS.2</t>
+          <t>Đổi lịch khám: AC-RS.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>AC-RS.2</t>
+          <t>AC-RS.1</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4639,39 +4639,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Given bệnh nhân có 3 lịch hẹn tương lai, When đổi một lịch, Then thành công (không vướng BR-03).</t>
+          <t>Given slot mới vừa bị người khác đặt, When đổi lịch, Then lịch cũ vẫn “booked” và không có lịch hẹn mới.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-SM.1</t>
+          <t>TC-AC-RS.2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Tóm tắt hồ sơ bệnh nhân bằng AI: AC-SM.1</t>
+          <t>Đổi lịch khám: AC-RS.2</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>AC-SM.1</t>
+          <t>AC-RS.2</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>scheduling</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4687,29 +4687,29 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>24021501-hunglk</t>
+          <t>qnt124</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Given bệnh nhân đã rút đồng ý AI, When bác sĩ bấm “Tóm tắt”, Then bị từ chối “consent-required”.</t>
+          <t>Given bệnh nhân có 3 lịch hẹn tương lai, When đổi một lịch, Then thành công (không vướng BR-03).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-SM.2</t>
+          <t>TC-AC-SM.1</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Tóm tắt hồ sơ bệnh nhân bằng AI: AC-SM.2</t>
+          <t>Tóm tắt hồ sơ bệnh nhân bằng AI: AC-SM.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>AC-SM.2</t>
+          <t>AC-SM.1</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4745,39 +4745,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Given yêu cầu gửi tới nhà cung cấp mô hình, Then không chứa họ tên, SĐT, email, địa chỉ của bệnh nhân (kiểm bằng test chặn mạng giả lập).</t>
+          <t>Given bệnh nhân đã rút đồng ý AI, When bác sĩ bấm “Tóm tắt”, Then bị từ chối “consent-required”.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-SN.1</t>
+          <t>TC-AC-SM.2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Gửi nhắc lịch: AC-SN.1</t>
+          <t>Tóm tắt hồ sơ bệnh nhân bằng AI: AC-SM.2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>AC-SN.1</t>
+          <t>AC-SM.2</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4793,44 +4793,44 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>qnt124</t>
+          <t>24021501-hunglk</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Given tin nhắc gửi đi, Then không chứa lý do khám hay chẩn đoán.</t>
+          <t>Given yêu cầu gửi tới nhà cung cấp mô hình, Then không chứa họ tên, SĐT, email, địa chỉ của bệnh nhân (kiểm bằng test chặn mạng giả lập).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-SP.1</t>
+          <t>TC-AC-SN.1</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm bệnh nhân: AC-SP.1</t>
+          <t>Gửi nhắc lịch: AC-SN.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>AC-SP.1</t>
+          <t>AC-SN.1</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>clinical</t>
+          <t>system</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4846,141 +4846,141 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Her55chers</t>
+          <t>qnt124</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Given điều kiện “ng” (2 ký tự), When tìm, Then bị từ chối, không trả danh sách.</t>
+          <t>Given tin nhắc gửi đi, Then không chứa lý do khám hay chẩn đoán.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>TC-AC-SP.1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Tìm kiếm bệnh nhân: AC-SP.1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>AC-SP.1</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Her55chers</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Given điều kiện “ng” (2 ký tự), When tìm, Then bị từ chối, không trả danh sách.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>TC-AC-SR.1</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Lên lịch nhắc khi lịch hẹn được tạo: AC-SR.1</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>AC-SR.1</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>MongoInboxIdempotencyTest.java::sameEventDeliveredTwiceIsHandledOnce
 InboxTest.java::sameEventDeliveredTwiceIsHandledOnce</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>qnt124</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>Given cùng sự kiện “đã đặt lịch” được giao 2 lần, Then chỉ có một bộ lần nhắc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TC-AC-ST.1</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Tạo lịch làm việc và mẫu lịch tuần: AC-ST.1</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>AC-ST.1</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>scheduling</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>qnt124</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Given mẫu 08:00–11:30 slot 15 phút, When lưu, Then hợp lệ; Given 08:00–11:20 slot 15 phút, Then báo lỗi chia không hết.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-TL.1</t>
+          <t>TC-AC-ST.1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Xem hồ sơ và timeline bệnh nhân: AC-TL.1</t>
+          <t>Tạo lịch làm việc và mẫu lịch tuần: AC-ST.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>AC-TL.1</t>
+          <t>AC-ST.1</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>clinical</t>
+          <t>scheduling</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Her55chers</t>
+          <t>qnt124</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Given bệnh nhân có lần khám “in-progress”, When bệnh nhân xem timeline, Then không thấy lần khám đó.</t>
+          <t>Given mẫu 08:00–11:30 slot 15 phút, When lưu, Then hợp lệ; Given 08:00–11:20 slot 15 phút, Then báo lỗi chia không hết.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-TL.2</t>
+          <t>TC-AC-TL.1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Xem hồ sơ và timeline bệnh nhân: AC-TL.2</t>
+          <t>Xem hồ sơ và timeline bệnh nhân: AC-TL.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AC-TL.2</t>
+          <t>AC-TL.1</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5064,29 +5064,29 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Given quản trị viên, When gọi API timeline, Then bị từ chối.</t>
+          <t>Given bệnh nhân có lần khám “in-progress”, When bệnh nhân xem timeline, Then không thấy lần khám đó.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-UD.1</t>
+          <t>TC-AC-TL.2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Upload tài liệu lâm sàng: AC-UD.1</t>
+          <t>Xem hồ sơ và timeline bệnh nhân: AC-TL.2</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AC-UD.1</t>
+          <t>AC-TL.2</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5117,24 +5117,24 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Given tệp 21 MB, When xin link upload, Then bị từ chối “file-too-large”.</t>
+          <t>Given quản trị viên, When gọi API timeline, Then bị từ chối.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-UD.2</t>
+          <t>TC-AC-UD.1</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Upload tài liệu lâm sàng: AC-UD.2</t>
+          <t>Upload tài liệu lâm sàng: AC-UD.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AC-UD.2</t>
+          <t>AC-UD.1</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5170,34 +5170,34 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Given tệp chứa mẫu EICAR, When upload, Then tài liệu “quarantined” và không phát sự kiện.</t>
+          <t>Given tệp 21 MB, When xin link upload, Then bị từ chối “file-too-large”.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-UP.1</t>
+          <t>TC-AC-UD.2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật thông tin hành chính: AC-UP.1</t>
+          <t>Upload tài liệu lâm sàng: AC-UD.2</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>AC-UP.1</t>
+          <t>AC-UD.2</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>clinical</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5223,29 +5223,29 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Given bệnh nhân gửi yêu cầu sửa ngày sinh, Then bị từ chối, dữ liệu không đổi.</t>
+          <t>Given tệp chứa mẫu EICAR, When upload, Then tài liệu “quarantined” và không phát sự kiện.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-VD.1</t>
+          <t>TC-AC-UP.1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Đánh dấu tài liệu nhập nhầm: AC-VD.1</t>
+          <t>Cập nhật thông tin hành chính: AC-UP.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>AC-VD.1</t>
+          <t>AC-UP.1</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5276,29 +5276,29 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Given tài liệu bị đánh dấu nhập nhầm, Then không xuất hiện trong danh sách mặc định nhưng vẫn truy vết được trong audit.</t>
+          <t>Given bệnh nhân gửi yêu cầu sửa ngày sinh, Then bị từ chối, dữ liệu không đổi.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-VT.1</t>
+          <t>TC-AC-VD.1</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ghi sinh hiệu: AC-VT.1</t>
+          <t>Đánh dấu tài liệu nhập nhầm: AC-VD.1</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>AC-VT.1</t>
+          <t>AC-VD.1</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>clinical</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5329,24 +5329,24 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Given SpO2 = 120, When lưu, Then báo lỗi tại trường, không lưu.</t>
+          <t>Given tài liệu bị đánh dấu nhập nhầm, Then không xuất hiện trong danh sách mặc định nhưng vẫn truy vết được trong audit.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TC-AC-VT.2</t>
+          <t>TC-AC-VT.1</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ghi sinh hiệu: AC-VT.2</t>
+          <t>Ghi sinh hiệu: AC-VT.1</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>AC-VT.2</t>
+          <t>AC-VT.1</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5382,77 +5382,77 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Given bác sĩ không có quan hệ điều trị, When ghi sinh hiệu, Then bị từ chối và ghi audit “deny”.</t>
+          <t>Given SpO2 = 120, When lưu, Then báo lỗi tại trường, không lưu.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A1</t>
+          <t>TC-AC-VT.2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>NFR-A1 SLO API đặt lịch và hồ sơ</t>
+          <t>Ghi sinh hiệu: AC-VT.2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>NFR-A1</t>
+          <t>AC-VT.2</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>nfr</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>viethung12062005</t>
+          <t>Her55chers</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 99,9%/tháng (≤ 43 phút). Cách đo: SLI từ gateway; dashboard error budget</t>
+          <t>Given bác sĩ không có quan hệ điều trị, When ghi sinh hiệu, Then bị từ chối và ghi audit “deny”.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A2</t>
+          <t>TC-NFR-A1</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>NFR-A2 SLO tính năng AI</t>
+          <t>NFR-A1 SLO API đặt lịch và hồ sơ</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>NFR-A2</t>
+          <t>NFR-A1</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5472,13 +5472,13 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5488,24 +5488,24 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 99,0%/tháng; AI lỗi không làm hỏng luồng khám. Cách đo: SLI + failure test tắt model</t>
+          <t>Chỉ số: 99,9%/tháng (≤ 43 phút). Cách đo: SLI từ gateway; dashboard error budget</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A3</t>
+          <t>TC-NFR-A2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>NFR-A3 Mất một zone</t>
+          <t>NFR-A2 SLO tính năng AI</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>NFR-A3</t>
+          <t>NFR-A2</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5541,24 +5541,24 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Không mất dữ liệu đã commit; phục hồi ≤ 5 phút. Cách đo: Cordon toàn bộ node một zone</t>
+          <t>Chỉ số: 99,0%/tháng; AI lỗi không làm hỏng luồng khám. Cách đo: SLI + failure test tắt model</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A4</t>
+          <t>TC-NFR-A3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>NFR-A4 RPO/RTO lâm sàng và lịch hẹn</t>
+          <t>NFR-A3 Mất một zone</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>NFR-A4</t>
+          <t>NFR-A3</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5594,24 +5594,24 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: RPO ≤ 5 phút; RTO ≤ 1 giờ. Cách đo: Diễn tập khôi phục có biên bản</t>
+          <t>Chỉ số: Không mất dữ liệu đã commit; phục hồi ≤ 5 phút. Cách đo: Cordon toàn bộ node một zone</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A5</t>
+          <t>TC-NFR-A4</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>NFR-A5 RPO tài liệu và audit</t>
+          <t>NFR-A4 RPO/RTO lâm sàng và lịch hẹn</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>NFR-A5</t>
+          <t>NFR-A4</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5647,24 +5647,24 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: RPO = 0 cho dữ liệu đã xác nhận ghi. Cách đo: Lưu trữ dư thừa theo zone; kiểm tra sau failover</t>
+          <t>Chỉ số: RPO ≤ 5 phút; RTO ≤ 1 giờ. Cách đo: Diễn tập khôi phục có biên bản</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A6</t>
+          <t>TC-NFR-A5</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>NFR-A6 Phụ thuộc bên ngoài lỗi</t>
+          <t>NFR-A5 RPO tài liệu và audit</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>NFR-A6</t>
+          <t>NFR-A5</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5700,24 +5700,24 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Không mất dữ liệu; retry + dead-letter; có fallback. Cách đo: Giả lập SMS/LLM/ML lỗi</t>
+          <t>Chỉ số: RPO = 0 cho dữ liệu đã xác nhận ghi. Cách đo: Lưu trữ dư thừa theo zone; kiểm tra sau failover</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-A7</t>
+          <t>TC-NFR-A6</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>NFR-A7 Deploy không gián đoạn</t>
+          <t>NFR-A6 Phụ thuộc bên ngoài lỗi</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>NFR-A7</t>
+          <t>NFR-A6</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5753,24 +5753,24 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 0 request lỗi do deploy. Cách đo: k6 chạy trong lúc rolling/canary</t>
+          <t>Chỉ số: Không mất dữ liệu; retry + dead-letter; có fallback. Cách đo: Giả lập SMS/LLM/ML lỗi</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI1</t>
+          <t>TC-NFR-A7</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI1 Truy xuất RAG</t>
+          <t>NFR-A7 Deploy không gián đoạn</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI1</t>
+          <t>NFR-A7</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Recall@5 ≥ 0,8; MRR ≥ 0,6. Cách đo: Bộ eval ≥ 100 câu hỏi</t>
+          <t>Chỉ số: 0 request lỗi do deploy. Cách đo: k6 chạy trong lúc rolling/canary</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI2</t>
+          <t>TC-NFR-AI1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI2 Câu trả lời RAG</t>
+          <t>NFR-AI1 Truy xuất RAG</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI2</t>
+          <t>NFR-AI1</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5859,24 +5859,24 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Groundedness ≥ 0,9; độ đúng trích dẫn ≥ 0,9; từ chối đúng khi không có nguồn ≥ 0,9. Cách đo: Eval harness</t>
+          <t>Chỉ số: Recall@5 ≥ 0,8; MRR ≥ 0,6. Cách đo: Bộ eval ≥ 100 câu hỏi</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI3</t>
+          <t>TC-NFR-AI2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI3 Prompt injection</t>
+          <t>NFR-AI2 Câu trả lời RAG</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI3</t>
+          <t>NFR-AI2</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5912,24 +5912,24 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 0 lần vượt rào trên ≥ 50 mẫu. Cách đo: Bộ tấn công tự động</t>
+          <t>Chỉ số: Groundedness ≥ 0,9; độ đúng trích dẫn ≥ 0,9; từ chối đúng khi không có nguồn ≥ 0,9. Cách đo: Eval harness</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI4</t>
+          <t>TC-NFR-AI3</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI4 Trích xuất</t>
+          <t>NFR-AI3 Prompt injection</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI4</t>
+          <t>NFR-AI3</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5965,24 +5965,24 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: F1 mức trường ≥ 0,85. Cách đo: Bộ tài liệu giả có nhãn</t>
+          <t>Chỉ số: 0 lần vượt rào trên ≥ 50 mẫu. Cách đo: Bộ tấn công tự động</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI5</t>
+          <t>TC-NFR-AI4</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI5 Chatbot đặt lịch</t>
+          <t>NFR-AI4 Trích xuất</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI5</t>
+          <t>NFR-AI4</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6018,24 +6018,24 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Hoàn thành ≥ 85%; 0 hành động không được xác nhận. Cách đo: Kịch bản hội thoại tự động</t>
+          <t>Chỉ số: F1 mức trường ≥ 0,85. Cách đo: Bộ tài liệu giả có nhãn</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI6</t>
+          <t>TC-NFR-AI5</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI6 Mô hình no-show</t>
+          <t>NFR-AI5 Chatbot đặt lịch</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI6</t>
+          <t>NFR-AI5</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6071,24 +6071,24 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: AUC ≥ 0,75 và hơn baseline; theo dõi drift hằng tuần. Cách đo: Đánh giá offline + giám sát</t>
+          <t>Chỉ số: Hoàn thành ≥ 85%; 0 hành động không được xác nhận. Cách đo: Kịch bản hội thoại tự động</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-AI7</t>
+          <t>TC-NFR-AI6</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI7 Fallback</t>
+          <t>NFR-AI6 Mô hình no-show</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI7</t>
+          <t>NFR-AI6</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6124,24 +6124,24 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Mỗi model trong chuỗi đều được eval. Cách đo: Báo cáo theo model</t>
+          <t>Chỉ số: AUC ≥ 0,75 và hơn baseline; theo dõi drift hằng tuần. Cách đo: Đánh giá offline + giám sát</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-C1</t>
+          <t>TC-NFR-AI7</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>NFR-C1 Ngân sách hạ tầng</t>
+          <t>NFR-AI7 Fallback</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>NFR-C1</t>
+          <t>NFR-AI7</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6161,13 +6161,13 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -6177,24 +6177,24 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Không có cụm thường trực; tài nguyên thường trực ≤ 10 USD/tháng; môi trường dựng khi cần. Cách đo: Báo cáo chi phí Azure theo tag</t>
+          <t>Chỉ số: Mỗi model trong chuỗi đều được eval. Cách đo: Báo cáo theo model</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-C2</t>
+          <t>TC-NFR-C1</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>NFR-C2 Chi phí AI</t>
+          <t>NFR-C1 Ngân sách hạ tầng</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>NFR-C2</t>
+          <t>NFR-C1</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -6230,24 +6230,24 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: ≤ 0,005 USD/request RAG; hạn mức token theo ngày và cảnh báo. Cách đo: Metric token/chi phí</t>
+          <t>Chỉ số: Không có cụm thường trực; tài nguyên thường trực ≤ 10 USD/tháng; môi trường dựng khi cần. Cách đo: Báo cáo chi phí Azure theo tag</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-C3</t>
+          <t>TC-NFR-C2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>NFR-C3 Minh bạch chi phí</t>
+          <t>NFR-C2 Chi phí AI</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>NFR-C3</t>
+          <t>NFR-C2</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6283,24 +6283,24 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Tag chi phí theo môi trường/service; báo cáo hằng tuần. Cách đo: Rà soát</t>
+          <t>Chỉ số: ≤ 0,005 USD/request RAG; hạn mức token theo ngày và cảnh báo. Cách đo: Metric token/chi phí</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-D1</t>
+          <t>TC-NFR-C3</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>NFR-D1 Lead time</t>
+          <t>NFR-C3 Minh bạch chi phí</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>NFR-D1</t>
+          <t>NFR-C3</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -6320,40 +6320,40 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Cần số liệu pipeline có triển khai thật (Azure).</t>
+          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>viethung12062005</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Commit → image đã ký ≤ 15 phút; → UAT ≤ 30 phút. Cách đo: Thống kê pipeline</t>
+          <t>Chỉ số: Tag chi phí theo môi trường/service; báo cáo hằng tuần. Cách đo: Rà soát</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-D2</t>
+          <t>TC-NFR-D1</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>NFR-D2 Rollback</t>
+          <t>NFR-D1 Lead time</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>NFR-D2</t>
+          <t>NFR-D1</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Cần cụm và Argo CD (ENV-01).</t>
+          <t>Cần số liệu pipeline có triển khai thật (Azure).</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6389,24 +6389,24 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: ≤ 5 phút bằng một thao tác (GitOps revert). Cách đo: Diễn tập rollback</t>
+          <t>Chỉ số: Commit → image đã ký ≤ 15 phút; → UAT ≤ 30 phút. Cách đo: Thống kê pipeline</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-D3</t>
+          <t>TC-NFR-D2</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>NFR-D3 Hạ tầng dưới dạng code</t>
+          <t>NFR-D2 Rollback</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>NFR-D3</t>
+          <t>NFR-D2</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Cần subscription Azure để chạy env-provision/env-destroy.</t>
+          <t>Cần cụm và Argo CD (ENV-01).</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6442,24 +6442,24 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 100% hạ tầng tạo bằng IaC; dựng lại được từ đầu. Cách đo: Dựng/hủy môi trường bằng workflow</t>
+          <t>Chỉ số: ≤ 5 phút bằng một thao tác (GitOps revert). Cách đo: Diễn tập rollback</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-D4</t>
+          <t>TC-NFR-D3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>NFR-D4 Cách ly môi trường</t>
+          <t>NFR-D3 Hạ tầng dưới dạng code</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>NFR-D4</t>
+          <t>NFR-D3</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6479,40 +6479,40 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
+          <t>Cần subscription Azure để chạy env-provision/env-destroy.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>viethung12062005</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: prod tách cụm và resource group với uat; dev chạy local. Cách đo: Rà soát cấu hình</t>
+          <t>Chỉ số: 100% hạ tầng tạo bằng IaC; dựng lại được từ đầu. Cách đo: Dựng/hủy môi trường bằng workflow</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-I1</t>
+          <t>TC-NFR-D4</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>NFR-I1 Chuẩn dữ liệu</t>
+          <t>NFR-D4 Cách ly môi trường</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>NFR-I1</t>
+          <t>NFR-D4</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6532,17 +6532,13 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>test_validators.py::def test_</t>
-        </is>
-      </c>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Contract test OpenAPI/schema sự kiện có; chưa validate tài nguyên FHIR bằng validator FHIR.</t>
+          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6552,24 +6548,24 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: API theo FHIR R4 cho các resource trong phạm vi. Cách đo: Validator FHIR trong test hợp đồng</t>
+          <t>Chỉ số: prod tách cụm và resource group với uat; dev chạy local. Cách đo: Rà soát cấu hình</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-I2</t>
+          <t>TC-NFR-I1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>NFR-I2 Client</t>
+          <t>NFR-I1 Chuẩn dữ liệu</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>NFR-I2</t>
+          <t>NFR-I1</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6579,7 +6575,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -6589,13 +6585,17 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>test_validators.py::def test_</t>
+        </is>
+      </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Contract test OpenAPI/schema sự kiện có; chưa validate tài nguyên FHIR bằng validator FHIR.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6605,24 +6605,24 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Web dùng được trên desktop và mobile (Chrome, Edge, Safari – 2 phiên bản gần nhất), màn hình ≥ 360 px. Cách đo: Test E2E đa trình duyệt</t>
+          <t>Chỉ số: API theo FHIR R4 cho các resource trong phạm vi. Cách đo: Validator FHIR trong test hợp đồng</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-I3</t>
+          <t>TC-NFR-I2</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>NFR-I3 Hạ tầng</t>
+          <t>NFR-I2 Client</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>NFR-I3</t>
+          <t>NFR-I2</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -6658,24 +6658,24 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Chạy trên Kubernetes bất kỳ (AKS là đích) và local. Cách đo: Chạy cùng chart trên kind và AKS</t>
+          <t>Chỉ số: Web dùng được trên desktop và mobile (Chrome, Edge, Safari – 2 phiên bản gần nhất), màn hình ≥ 360 px. Cách đo: Test E2E đa trình duyệt</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-O1</t>
+          <t>TC-NFR-I3</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>NFR-O1 Tracing phân tán</t>
+          <t>NFR-I3 Hạ tầng</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>NFR-O1</t>
+          <t>NFR-I3</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -6695,17 +6695,13 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>ServiceDefaultsTest.java::otlpExportIsOffUnlessClusterEnablesIt</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Chưa kiểm trace xuyên service.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6715,24 +6711,24 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: 100% request có trace xuyên service. Cách đo: Kiểm tra trace mẫu qua gateway → service → bus</t>
+          <t>Chỉ số: Chạy trên Kubernetes bất kỳ (AKS là đích) và local. Cách đo: Chạy cùng chart trên kind và AKS</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-O2</t>
+          <t>TC-NFR-O1</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>NFR-O2 Dashboard SLO</t>
+          <t>NFR-O1 Tracing phân tán</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>NFR-O2</t>
+          <t>NFR-O1</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6742,7 +6738,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -6752,13 +6748,17 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>ServiceDefaultsTest.java::otlpExportIsOffUnlessClusterEnablesIt</t>
+        </is>
+      </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
+          <t>Chưa kiểm trace xuyên service.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6768,24 +6768,24 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Dashboard SLI/SLO + error budget cho A1, P1, P2. Cách đo: Rà soát dashboard</t>
+          <t>Chỉ số: 100% request có trace xuyên service. Cách đo: Kiểm tra trace mẫu qua gateway → service → bus</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-O3</t>
+          <t>TC-NFR-O2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>NFR-O3 Cảnh báo</t>
+          <t>NFR-O2 Dashboard SLO</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>NFR-O3</t>
+          <t>NFR-O2</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -6805,13 +6805,13 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6821,24 +6821,24 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Cảnh báo burn rate, hàng lỗi có tin, chứng chỉ sắp hết hạn, truy cập khẩn cấp. Cách đo: Kích hoạt từng điều kiện cảnh báo</t>
+          <t>Chỉ số: Dashboard SLI/SLO + error budget cho A1, P1, P2. Cách đo: Rà soát dashboard</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-O4</t>
+          <t>TC-NFR-O3</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>NFR-O4 Log</t>
+          <t>NFR-O3 Cảnh báo</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>NFR-O4</t>
+          <t>NFR-O3</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6858,17 +6858,13 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>ServiceDefaultsTest.java::healthDoesNotLeakDetails</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Chưa quét log tìm PII.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6878,24 +6874,24 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Log có cấu trúc, có trace-id, không chứa PII. Cách đo: Test quét log (NFR-SEC13)</t>
+          <t>Chỉ số: Cảnh báo burn rate, hàng lỗi có tin, chứng chỉ sắp hết hạn, truy cập khẩn cấp. Cách đo: Kích hoạt từng điều kiện cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P1</t>
+          <t>TC-NFR-O4</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>NFR-P1 Tìm slot trống</t>
+          <t>NFR-O4 Log</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>NFR-P1</t>
+          <t>NFR-O4</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6905,7 +6901,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6920,12 +6916,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>slots-search.js::p(95)&lt;300</t>
+          <t>ServiceDefaultsTest.java::healthDoesNotLeakDetails</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Script đã có và kiểm cú pháp trong CI; chạy trên UAT cỡ production khi có Azure (PRD-10, PRD-01).</t>
+          <t>Chưa quét log tìm PII.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6935,24 +6931,24 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: p95 ≤ 300 ms tại 500 RPS. Cách đo: k6, 10 phút, tại gateway; tỉ lệ lỗi &lt; 0,1%</t>
+          <t>Chỉ số: Log có cấu trúc, có trace-id, không chứa PII. Cách đo: Test quét log (NFR-SEC13)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P2</t>
+          <t>TC-NFR-P1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>NFR-P2 Đặt lịch</t>
+          <t>NFR-P1 Tìm slot trống</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>NFR-P2</t>
+          <t>NFR-P1</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -6977,12 +6973,12 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>booking.js::p(95)&lt;800</t>
+          <t>slots-search.js::p(95)&lt;300</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Như trên.</t>
+          <t>Script đã có và kiểm cú pháp trong CI; chạy trên UAT cỡ production khi có Azure (PRD-10, PRD-01).</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6992,24 +6988,24 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: p95 ≤ 800 ms tại 50 RPS; lỗi 5xx &lt; 0,1%. Cách đo: k6, 10 phút, kèm 20% yêu cầu tranh chấp cùng slot</t>
+          <t>Chỉ số: p95 ≤ 300 ms tại 500 RPS. Cách đo: k6, 10 phút, tại gateway; tỉ lệ lỗi &lt; 0,1%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P3</t>
+          <t>TC-NFR-P2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>NFR-P3 Mở hồ sơ / timeline</t>
+          <t>NFR-P2 Đặt lịch</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>NFR-P3</t>
+          <t>NFR-P2</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -7029,13 +7025,17 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>booking.js::p(95)&lt;800</t>
+        </is>
+      </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Như trên.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7045,24 +7045,24 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: p95 ≤ 500 ms. Cách đo: k6 + trace, bệnh nhân có 50 lần khám</t>
+          <t>Chỉ số: p95 ≤ 800 ms tại 50 RPS; lỗi 5xx &lt; 0,1%. Cách đo: k6, 10 phút, kèm 20% yêu cầu tranh chấp cùng slot</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P4</t>
+          <t>TC-NFR-P3</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>NFR-P4 Cấp link upload/tải</t>
+          <t>NFR-P3 Mở hồ sơ / timeline</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>NFR-P4</t>
+          <t>NFR-P3</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7098,24 +7098,24 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: p95 ≤ 300 ms. Cách đo: k6</t>
+          <t>Chỉ số: p95 ≤ 500 ms. Cách đo: k6 + trace, bệnh nhân có 50 lần khám</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P5</t>
+          <t>TC-NFR-P4</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>NFR-P5 Trợ lý RAG</t>
+          <t>NFR-P4 Cấp link upload/tải</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>NFR-P5</t>
+          <t>NFR-P4</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -7151,24 +7151,24 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Token đầu ≤ 3 s; trả lời đủ ≤ 10 s (p95). Cách đo: Eval harness + trace, 100 câu hỏi</t>
+          <t>Chỉ số: p95 ≤ 300 ms. Cách đo: k6</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P6</t>
+          <t>TC-NFR-P5</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>NFR-P6 Tóm tắt hồ sơ</t>
+          <t>NFR-P5 Trợ lý RAG</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>NFR-P6</t>
+          <t>NFR-P5</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -7204,24 +7204,24 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: ≤ 15 s (p95). Cách đo: Eval harness</t>
+          <t>Chỉ số: Token đầu ≤ 3 s; trả lời đủ ≤ 10 s (p95). Cách đo: Eval harness + trace, 100 câu hỏi</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P7</t>
+          <t>TC-NFR-P6</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>NFR-P7 Trích xuất tài liệu</t>
+          <t>NFR-P6 Tóm tắt hồ sơ</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>NFR-P7</t>
+          <t>NFR-P6</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -7257,24 +7257,24 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: ≤ 2 phút từ lúc upload (p95). Cách đo: Metric độ trễ hàng đợi</t>
+          <t>Chỉ số: ≤ 15 s (p95). Cách đo: Eval harness</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-P8</t>
+          <t>TC-NFR-P7</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>NFR-P8 Gửi nhắc lịch</t>
+          <t>NFR-P7 Trích xuất tài liệu</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>NFR-P8</t>
+          <t>NFR-P7</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -7310,24 +7310,24 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: ≥ 99% gửi trong 5 phút sau giờ hẹn gửi. Cách đo: Metric notification trên 1.000 lần nhắc</t>
+          <t>Chỉ số: ≤ 2 phút từ lúc upload (p95). Cách đo: Metric độ trễ hàng đợi</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-S1</t>
+          <t>TC-NFR-P8</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>NFR-S1 Đợt tăng tải 07:00</t>
+          <t>NFR-P8 Gửi nhắc lịch</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>NFR-S1</t>
+          <t>NFR-P8</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -7353,34 +7353,34 @@
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Cần KEDA/HPA trên UAT (PRD-11).</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>viethung12062005</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Tự scale đủ tải trong ≤ 2 phút, không can thiệp tay. Cách đo: k6 ramp 0 → 500 RPS trong 1 phút; KEDA cron + HPA</t>
+          <t>Chỉ số: ≥ 99% gửi trong 5 phút sau giờ hẹn gửi. Cách đo: Metric notification trên 1.000 lần nhắc</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-S2</t>
+          <t>TC-NFR-S1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>NFR-S2 Tải 5×</t>
+          <t>NFR-S1 Đợt tăng tải 07:00</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>NFR-S2</t>
+          <t>NFR-S1</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -7400,44 +7400,40 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>slots-search.js::scenarios</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Kịch bản 5× nằm trong script; chạy khi có UAT.</t>
+          <t>Cần KEDA/HPA trên UAT (PRD-11).</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>viethung12062005</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: p95 không vượt 2× mục tiêu P1/P2. Cách đo: k6</t>
+          <t>Chỉ số: Tự scale đủ tải trong ≤ 2 phút, không can thiệp tay. Cách đo: k6 ramp 0 → 500 RPS trong 1 phút; KEDA cron + HPA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-S3</t>
+          <t>TC-NFR-S2</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>NFR-S3 Tải 10×</t>
+          <t>NFR-S2 Tải 5×</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>NFR-S3</t>
+          <t>NFR-S2</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -7467,7 +7463,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Kịch bản 10×; chạy khi có UAT.</t>
+          <t>Kịch bản 5× nằm trong script; chạy khi có UAT.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7477,24 +7473,24 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Xuống cấp có kiểm soát (429, hàng chờ) thay vì sập. Cách đo: k6; không có pod restart do OOM</t>
+          <t>Chỉ số: p95 không vượt 2× mục tiêu P1/P2. Cách đo: k6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-S4</t>
+          <t>TC-NFR-S3</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>NFR-S4 Scale độc lập</t>
+          <t>NFR-S3 Tải 10×</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>NFR-S4</t>
+          <t>NFR-S3</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -7514,13 +7510,17 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>slots-search.js::scenarios</t>
+        </is>
+      </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Kịch bản 10×; chạy khi có UAT.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7530,136 +7530,136 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Tải AI/tài liệu không làm P1/P2 vượt mục tiêu. Cách đo: k6 chạy song song tải AI và đặt lịch</t>
+          <t>Chỉ số: Xuống cấp có kiểm soát (429, hàng chờ) thay vì sập. Cách đo: k6; không có pod restart do OOM</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>TC-NFR-S4</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>NFR-S4 Scale độc lập</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>NFR-S4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>nfr</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ số: Tải AI/tài liệu không làm P1/P2 vượt mục tiêu. Cách đo: k6 chạy song song tải AI và đặt lịch</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
           <t>TC-NFR-SEC1</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC1 Xác thực</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC1</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>nfr</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>WebTest.java::wrongAudienceWrongSignatureAndExpiredTokensAre401
 WebTest.java::staffWithoutMfaIsRejectedAndWithMfaAccepted
 WebTest.java::patientDoesNotNeedMfa</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>Chưa thử với Keycloak/Entra thật; chưa đo thời hạn token ≤ 15 phút từ IdP.</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Chưa thử với Keycloak thật; chưa đo thời hạn token ≤ 15 phút từ IdP.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>Chỉ số: OIDC + PKCE; nhân viên bắt buộc MFA; access token ≤ 15 phút; không lưu mật khẩu. Cách đo: Test tích hợp với IdP; kiểm tra claim MFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>TC-NFR-SEC10</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC10 Tối thiểu hóa dữ liệu</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC10</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>nfr</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ số: Chỉ thu thập trường cần cho mục đích đã nêu; kết quả tìm kiếm và danh sách che SĐT, không có chẩn đoán. Cách đo: Rà soát schema API; test kết quả tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC11</t>
+          <t>TC-NFR-SEC10</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC11 Đồng ý xử lý dữ liệu</t>
+          <t>NFR-SEC10 Tối thiểu hóa dữ liệu</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC11</t>
+          <t>NFR-SEC10</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -7695,24 +7695,24 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Lưu đồng ý có phiên bản và thời điểm; rút đồng ý có hiệu lực ngay cho mọi xử lý AI. Cách đo: Test rút đồng ý rồi gọi tóm tắt/trích xuất/dự đoán</t>
+          <t>Chỉ số: Chỉ thu thập trường cần cho mục đích đã nêu; kết quả tìm kiếm và danh sách che SĐT, không có chẩn đoán. Cách đo: Rà soát schema API; test kết quả tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC12</t>
+          <t>TC-NFR-SEC11</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC12 Quyền chủ thể dữ liệu</t>
+          <t>NFR-SEC11 Đồng ý xử lý dữ liệu</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC12</t>
+          <t>NFR-SEC11</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7748,24 +7748,24 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Bệnh nhân xem được lịch sử truy cập hồ sơ và yêu cầu bản sao dữ liệu; DPO xử lý có theo dõi thời hạn. Cách đo: Test luồng end-to-end</t>
+          <t>Chỉ số: Lưu đồng ý có phiên bản và thời điểm; rút đồng ý có hiệu lực ngay cho mọi xử lý AI. Cách đo: Test rút đồng ý rồi gọi tóm tắt/trích xuất/dự đoán</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC13</t>
+          <t>TC-NFR-SEC12</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC13 Không để lộ dữ liệu</t>
+          <t>NFR-SEC12 Quyền chủ thể dữ liệu</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC13</t>
+          <t>NFR-SEC12</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -7801,24 +7801,24 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Không PII/PHI trong log, metric, trace, sự kiện, URL, thông báo lỗi; lỗi không lộ sự tồn tại hồ sơ (404). Cách đo: Test quét log/sự kiện trong test tích hợp tìm mẫu PII; test 404 cho tài nguyên của người khác</t>
+          <t>Chỉ số: Bệnh nhân xem được lịch sử truy cập hồ sơ và yêu cầu bản sao dữ liệu; DPO xử lý có theo dõi thời hạn. Cách đo: Test luồng end-to-end</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC14</t>
+          <t>TC-NFR-SEC13</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC14 Phiên làm việc</t>
+          <t>NFR-SEC13 Không để lộ dữ liệu</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC14</t>
+          <t>NFR-SEC13</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -7854,131 +7854,131 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Nhân viên tự đăng xuất sau 15 phút không thao tác, bệnh nhân 30 phút; đăng nhập lại tối đa sau 12 giờ (nhân viên) / 24 giờ (bệnh nhân); token không lưu localStorage. Cách đo: Test E2E giao diện. Chặt hơn mức tối đa của NIST SP 800-63B-4 mức AAL2 (không thao tác 1 giờ, tổng 24 giờ) vì máy dùng chung tại phòng khám</t>
+          <t>Chỉ số: Không PII/PHI trong log, metric, trace, sự kiện, URL, thông báo lỗi; lỗi không lộ sự tồn tại hồ sơ (404). Cách đo: Test quét log/sự kiện trong test tích hợp tìm mẫu PII; test 404 cho tài nguyên của người khác</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>TC-NFR-SEC14</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC14 Phiên làm việc</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC14</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>nfr</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>e2e</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ số: Nhân viên tự đăng xuất sau 15 phút không thao tác, bệnh nhân 30 phút; đăng nhập lại tối đa sau 12 giờ (nhân viên) / 24 giờ (bệnh nhân); token không lưu localStorage. Cách đo: Test E2E giao diện. Chặt hơn mức tối đa của NIST SP 800-63B-4 mức AAL2 (không thao tác 1 giờ, tổng 24 giờ) vì máy dùng chung tại phòng khám</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
           <t>TC-NFR-SEC15</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC15 Bảo vệ ứng dụng web</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC15</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>nfr</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>qa.yml::dast-web
 headers.spec.ts::TC-SEC-09</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
         <is>
           <t>Chỉ số: CSP chặt, HSTS, chống clickjacking, cookie Secure/HttpOnly/SameSite; không có lỗi mức High theo OWASP ZAP baseline. Cách đo: ZAP baseline trên UAT trong pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>TC-NFR-SEC16</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC16 Chống lạm dụng</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC16</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>nfr</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ số: Giới hạn tốc độ theo người dùng; khóa tạm sau 5 lần đăng nhập sai; tìm kiếm bệnh nhân không liệt kê toàn bộ. Cách đo: Test 429; test điều kiện tìm tối thiểu</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC17</t>
+          <t>TC-NFR-SEC16</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC17 An toàn tệp tải lên</t>
+          <t>NFR-SEC16 Chống lạm dụng</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC17</t>
+          <t>NFR-SEC16</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -8014,24 +8014,24 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Kiểm tra loại theo nội dung, ≤ 20 MB, quét mã độc trước khi dùng; tệp nhiễm bị cách ly. Cách đo: Test với EICAR, tệp đổi đuôi, tệp quá cỡ</t>
+          <t>Chỉ số: Giới hạn tốc độ theo người dùng; khóa tạm sau 5 lần đăng nhập sai; tìm kiếm bệnh nhân không liệt kê toàn bộ. Cách đo: Test 429; test điều kiện tìm tối thiểu</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC18</t>
+          <t>TC-NFR-SEC17</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC18 Phân tách nhiệm vụ</t>
+          <t>NFR-SEC17 An toàn tệp tải lên</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC18</t>
+          <t>NFR-SEC17</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -8067,24 +8067,24 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Quản trị viên/DPO không đọc dữ liệu lâm sàng; gán vai trò đặc quyền và khôi phục dữ liệu cần người thứ hai duyệt. Cách đo: Test phân quyền + rà soát quy trình</t>
+          <t>Chỉ số: Kiểm tra loại theo nội dung, ≤ 20 MB, quét mã độc trước khi dùng; tệp nhiễm bị cách ly. Cách đo: Test với EICAR, tệp đổi đuôi, tệp quá cỡ</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC19</t>
+          <t>TC-NFR-SEC18</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC19 Lưu trữ và xóa</t>
+          <t>NFR-SEC18 Phân tách nhiệm vụ</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC19</t>
+          <t>NFR-SEC18</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -8120,47 +8120,100 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Thời hạn lưu theo bảng lưu trữ; dữ liệu tạm tự xóa đúng hạn; hồ sơ bệnh án lưu dài hạn. Cách đo: Test job xóa dữ liệu hết hạn</t>
+          <t>Chỉ số: Quản trị viên/DPO không đọc dữ liệu lâm sàng; gán vai trò đặc quyền và khôi phục dữ liệu cần người thứ hai duyệt. Cách đo: Test phân quyền + rà soát quy trình</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>TC-NFR-SEC19</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC19 Lưu trữ và xóa</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC19</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>nfr</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ số: Thời hạn lưu theo bảng lưu trữ; dữ liệu tạm tự xóa đúng hạn; hồ sơ bệnh án lưu dài hạn. Cách đo: Test job xóa dữ liệu hết hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
           <t>TC-NFR-SEC2</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC2 Phân quyền</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC2</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>nfr</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>MatrixDrivenTest.java::adminAndDpoNeverReachClinicalResources
 MatrixDrivenTest.java::defaultDenyForRolesWithoutRuleEvenWhenEveryPredicateHolds
@@ -8169,89 +8222,36 @@
 web/e2e/booking.spec.ts::TC-NFR-SEC2-DPO DPO không thấy menu nghiệp vụ lâm sàng</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Mới ở mức thư viện quyết định và giao diện; chưa có test gọi từng endpoint thật (SCH-/CLN-/DOC-). Owner: D1, D2.</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr">
         <is>
           <t>Chỉ số: Đúng 100% ma trận phân quyền; mặc định từ chối. Cách đo: Test sinh từ contracts/authz/matrix.yaml: mỗi ô cho phép và từ chối; test 'mọi endpoint có quy tắc'</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>TC-NFR-SEC20</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC20 Ẩn danh dữ liệu phân tích/huấn luyện</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC20</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>nfr</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ số: Dữ liệu huấn luyện ML và báo cáo không chứa định danh trực tiếp; chỉ dữ liệu của bệnh nhân còn đồng ý. Cách đo: Test kiểm tra schema tập huấn luyện</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC21</t>
+          <t>TC-NFR-SEC20</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC21 Sự cố và chuyển dữ liệu ra nước ngoài</t>
+          <t>NFR-SEC20 Ẩn danh dữ liệu phân tích/huấn luyện</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC21</t>
+          <t>NFR-SEC20</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -8271,13 +8271,13 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -8287,24 +8287,24 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Thông báo vi phạm cho cơ quan chuyên trách chậm nhất 72 giờ kể từ khi phát hiện (Điều 23 khoản 1 Luật 91/2025/QH15); hồ sơ đánh giá tác động xử lý dữ liệu (Điều 21, nộp trong 60 ngày kể từ lần xử lý đầu tiên, cập nhật 6 tháng một lần theo Điều 22) và hồ sơ đánh giá tác động chuyển dữ liệu ra nước ngoài (Điều 20: vùng cloud ngoài Việt Nam, nhà cung cấp LLM nước ngoài) trước khi dùng dữ liệu thật. Cách đo: Runbook sự cố + diễn tập đo thời gian từ phát hiện đến thông báo; hồ sơ đánh giá tác động được duyệt</t>
+          <t>Chỉ số: Dữ liệu huấn luyện ML và báo cáo không chứa định danh trực tiếp; chỉ dữ liệu của bệnh nhân còn đồng ý. Cách đo: Test kiểm tra schema tập huấn luyện</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC3</t>
+          <t>TC-NFR-SEC21</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC3 Mã hóa</t>
+          <t>NFR-SEC21 Sự cố và chuyển dữ liệu ra nước ngoài</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC3</t>
+          <t>NFR-SEC21</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -8324,13 +8324,13 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Rà soát/đo thủ công theo kế hoạch kiểm thử.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -8340,24 +8340,24 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: TLS 1.2+ mọi kết nối kể cả nội bộ cụm; mã hóa at-rest mọi kho dữ liệu và bản sao lưu. Cách đo: Quét cấu hình TLS; kiểm tra cấu hình Terraform</t>
+          <t>Chỉ số: Thông báo vi phạm cho cơ quan chuyên trách chậm nhất 72 giờ kể từ khi phát hiện (Điều 23 khoản 1 Luật 91/2025/QH15); hồ sơ đánh giá tác động xử lý dữ liệu (Điều 21, nộp trong 60 ngày kể từ lần xử lý đầu tiên, cập nhật 6 tháng một lần theo Điều 22) và hồ sơ đánh giá tác động chuyển dữ liệu ra nước ngoài (Điều 20: vùng cloud ngoài Việt Nam, nhà cung cấp LLM nước ngoài) trước khi dùng dữ liệu thật. Cách đo: Runbook sự cố + diễn tập đo thời gian từ phát hiện đến thông báo; hồ sơ đánh giá tác động được duyệt</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC4</t>
+          <t>TC-NFR-SEC3</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC4 Secret</t>
+          <t>NFR-SEC3 Mã hóa</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC4</t>
+          <t>NFR-SEC3</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -8377,15 +8377,15 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>pr-checks.yml::pr-checks</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
@@ -8393,139 +8393,135 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Không secret trong code/config/image; Key Vault + workload identity; xoay vòng không cần deploy. Cách đo: gitleaks + push protection; diễn tập xoay khóa</t>
+          <t>Chỉ số: TLS 1.2+ mọi kết nối kể cả nội bộ cụm; mã hóa at-rest mọi kho dữ liệu và bản sao lưu. Cách đo: Quét cấu hình TLS; kiểm tra cấu hình Terraform</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>TC-NFR-SEC4</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC4 Secret</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>nfr</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>pr-checks.yml::pr-checks</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ số: Không secret trong code/config/image; Key Vault + workload identity; xoay vòng không cần deploy. Cách đo: gitleaks + push protection; diễn tập xoay khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
           <t>TC-NFR-SEC5</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC5 Audit</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC5</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>nfr</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>AuditTest.java::deniedDecisionIsAuditedWithReasonAndAllowedWithPurpose
 AuditSinkTest.java::auditSurvivesARolledBackBusinessTransaction</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Audit cho phép và từ chối đã kiểm ở thư viện; chưa đối chiếu 100% thao tác của từng service và độ trễ ≤ 1 phút (AUD-xx).</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>Chỉ số: 100% truy cập dữ liệu bệnh nhân được audit (cả từ chối); tra cứu được ≤ 1 phút; bất biến. Cách đo: Test đối chiếu thao tác ↔ bản ghi audit; thử sửa/xóa kho WORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>TC-NFR-SEC6</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC6 Chuỗi cung ứng</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC6</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>nfr</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>ci</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>svc-web.yml::container</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Trivy, SBOM, cosign chạy trong container.yml (repo templates); Kyverno chặn image không ký chỉ kiểm khi có cụm (GOP-07).</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ số: Image quét lỗ hổng (chặn High/Critical có bản vá), ký, có SBOM; cụm chỉ chạy image đã ký. Cách đo: Pipeline CI; Kyverno từ chối image không ký</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC7</t>
+          <t>TC-NFR-SEC6</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC7 Cô lập mạng</t>
+          <t>NFR-SEC6 Chuỗi cung ứng</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC7</t>
+          <t>NFR-SEC6</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -8535,7 +8531,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -8545,13 +8541,17 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>svc-web.yml::container</t>
+        </is>
+      </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Trivy, SBOM, cosign chạy trong container.yml (repo templates); Kyverno chặn image không ký chỉ kiểm khi có cụm (GOP-07).</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8561,24 +8561,24 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Mặc định chặn traffic giữa pod; CSDL không có endpoint public. Cách đo: Kiểm tra NetworkPolicy; thử kết nối trái phép</t>
+          <t>Chỉ số: Image quét lỗ hổng (chặn High/Critical có bản vá), ký, có SBOM; cụm chỉ chạy image đã ký. Cách đo: Pipeline CI; Kyverno từ chối image không ký</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC8</t>
+          <t>TC-NFR-SEC7</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC8 An toàn AI</t>
+          <t>NFR-SEC7 Cô lập mạng</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC8</t>
+          <t>NFR-SEC7</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>security</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Che PII trước khi gửi model bên ngoài; 0 lần vượt rào prompt injection; AI chỉ dùng quyền người gọi. Cách đo: Test chặn yêu cầu chứa PII; bộ 50 mẫu tấn công (NFR-AI3)</t>
+          <t>Chỉ số: Mặc định chặn traffic giữa pod; CSDL không có endpoint public. Cách đo: Kiểm tra NetworkPolicy; thử kết nối trái phép</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC9</t>
+          <t>TC-NFR-SEC8</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC9 Dữ liệu giả</t>
+          <t>NFR-SEC8 An toàn AI</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC9</t>
+          <t>NFR-SEC8</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -8651,15 +8651,15 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>00-synthetic-data.md::dữ liệu giả</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
@@ -8667,24 +8667,24 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Chỉ dữ liệu giả ở mọi môi trường. Cách đo: Công cụ sinh dữ liệu giả; rà soát</t>
+          <t>Chỉ số: Che PII trước khi gửi model bên ngoài; 0 lần vượt rào prompt injection; AI chỉ dùng quyền người gọi. Cách đo: Test chặn yêu cầu chứa PII; bộ 50 mẫu tấn công (NFR-AI3)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TC-NFR-U1</t>
+          <t>TC-NFR-SEC9</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>NFR-U1 Ngôn ngữ và trợ năng</t>
+          <t>NFR-SEC9 Dữ liệu giả</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>NFR-U1</t>
+          <t>NFR-SEC9</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -8694,29 +8694,25 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>review</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>automated</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>web/e2e/quality.spec.ts::TC-NFR-U1-LANG đổi ngôn ngữ sang tiếng Anh</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ kiểm ở giao diện với dữ liệu giả; chưa kiểm API/dịch vụ thật.</t>
-        </is>
-      </c>
+          <t>00-synthetic-data.md::dữ liệu giả</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
@@ -8724,50 +8720,54 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Chỉ số: Giao diện tiếng Việt và tiếng Anh; đạt WCAG 2.1 mức AA ở các màn hình bệnh nhân. Cách đo: axe-core trong test E2E</t>
+          <t>Chỉ số: Chỉ dữ liệu giả ở mọi môi trường. Cách đo: Công cụ sinh dữ liệu giả; rà soát</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-NFR-U1</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>IDOR: đọc hồ sơ, lịch hẹn, tài liệu của bệnh nhân khác bằng ID đoán được</t>
+          <t>NFR-U1 Ngôn ngữ và trợ năng</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC2, NFR-SEC13</t>
+          <t>NFR-U1</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>nfr</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>web/e2e/quality.spec.ts::TC-NFR-U1-LANG đổi ngôn ngữ sang tiếng Anh</t>
+        </is>
+      </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Chỉ kiểm ở giao diện với dữ liệu giả; chưa kiểm API/dịch vụ thật.</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8777,24 +8777,24 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Given bệnh nhân A đăng nhập, When gọi GET /fhir/Patient|Appointment|DocumentReference với ID của bệnh nhân B, Then nhận 404 (không phải 403), nội dung phản hồi giống hệt trường hợp ID không tồn tại, và có bản ghi audit 'deny'.</t>
+          <t>Chỉ số: Giao diện tiếng Việt và tiếng Anh; đạt WCAG 2.1 mức AA ở các màn hình bệnh nhân. Cách đo: axe-core trong test E2E</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-02</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Leo thang đặc quyền theo chiều dọc: bệnh nhân gọi API nhân viên, nhân viên gọi API quản trị</t>
+          <t>IDOR: đọc hồ sơ, lịch hẹn, tài liệu của bệnh nhân khác bằng ID đoán được</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC2</t>
+          <t>NFR-SEC2, NFR-SEC13</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -8814,17 +8814,13 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>MatrixDrivenTest.java::unknownResourceOrActionIsDenied</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Cần test sinh từ OpenAPI + ma trận gọi mọi endpoint theo từng vai trò (khi service có endpoint).</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8834,24 +8830,24 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Given mỗi vai trò, When gọi mọi endpoint không có trong ma trận phân quyền của vai trò đó, Then bị từ chối và ghi audit; test sinh từ contracts/authz/matrix.yaml và openapi.</t>
+          <t>Given bệnh nhân A đăng nhập, When gọi GET /fhir/Patient|Appointment|DocumentReference với ID của bệnh nhân B, Then nhận 404 (không phải 403), nội dung phản hồi giống hệt trường hợp ID không tồn tại, và có bản ghi audit 'deny'.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-SEC-02</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Mass assignment: gửi thêm trường status, patientId, role, createdBy trong body</t>
+          <t>Leo thang đặc quyền theo chiều dọc: bệnh nhân gọi API nhân viên, nhân viên gọi API quản trị</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC2, NFR-SEC10</t>
+          <t>NFR-SEC2</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -8871,13 +8867,17 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>MatrixDrivenTest.java::unknownResourceOrActionIsDenied</t>
+        </is>
+      </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Cần test sinh từ OpenAPI + ma trận gọi mọi endpoint theo từng vai trò (khi service có endpoint).</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8887,243 +8887,243 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Given body có thêm trường không thuộc schema (status, subject, role, id), Then bị từ chối 400; không trường lạ nào được lưu.</t>
+          <t>Given mỗi vai trò, When gọi mọi endpoint không có trong ma trận phân quyền của vai trò đó, Then bị từ chối và ghi audit; test sinh từ contracts/authz/matrix.yaml và openapi.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>TC-SEC-03</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Mass assignment: gửi thêm trường status, patientId, role, createdBy trong body</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC2, NFR-SEC10</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Given body có thêm trường không thuộc schema (status, subject, role, id), Then bị từ chối 400; không trường lạ nào được lưu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-04</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>JWT: chữ ký sai, alg=none, hết hạn, sai audience, sai issuer, thiếu claim roles</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC1</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>WebTest.java::wrongAudienceWrongSignatureAndExpiredTokensAre401
 WebTest.java::missingTokenIs401ProblemJson
 WebTest.java::tokenWithoutKnownRoleIs403</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>Thiếu ca alg=none và sai issuer; thêm vào WebTest.</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
+      <c r="K158" s="2" t="inlineStr">
         <is>
           <t>Given từng loại token lỗi, When gọi API, Then 401 với Problem Details; không rò rỉ lý do chi tiết.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>TC-SEC-05</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Vai trò chỉ lấy từ claim đã ký; header, query hay body không thể tự gán vai trò</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC1, NFR-SEC2</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Given request có header X-Role: admin hoặc tham số role=admin, Then bị bỏ qua; quyền vẫn theo token.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>TC-SEC-05</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Vai trò chỉ lấy từ claim đã ký; header, query hay body không thể tự gán vai trò</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC1, NFR-SEC2</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Given request có header X-Role: admin hoặc tham số role=admin, Then bị bỏ qua; quyền vẫn theo token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-06</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Nhân viên chưa có MFA không truy cập được dữ liệu bệnh nhân; token thiếu amr bị từ chối</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC1, AC-08.2</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>WebTest.java::staffWithoutMfaIsRejectedAndWithMfaAccepted
 WebTest.java::patientDoesNotNeedMfa</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
         <is>
           <t>Given token nhân viên không có claim MFA, When truy cập dữ liệu, Then 403 mfa-required; bệnh nhân không cần MFA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>TC-SEC-07</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Injection: ký tự đặc biệt trong tên, tìm kiếm, lý do khám (SQL, NoSQL, regex, LDAP)</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC2</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Given đầu vào chứa ', ", $where, {$ne:null}, .*, ${jndi:...}, Then được xử lý như văn bản thường; không đổi hành vi truy vấn; không lỗi 500.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-08</t>
+          <t>TC-SEC-07</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>XSS lưu trữ: script trong lý do khám, bệnh sử, tên, tên tệp</t>
+          <t>Injection: ký tự đặc biệt trong tên, tìm kiếm, lý do khám (SQL, NoSQL, regex, LDAP)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC15</t>
+          <t>NFR-SEC2</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -9143,17 +9143,13 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>web/e2e/booking.spec.ts::TC-SEC-08 văn bản độc hại trong lý do khám được hiển thị như</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Chỉ kiểm ở giao diện với dữ liệu giả; chưa kiểm API/dịch vụ thật.</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -9163,47 +9159,104 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Given văn bản chứa &lt;script&gt; hoặc onerror=, When hiển thị trên mọi màn hình, Then được mã hóa; không thực thi mã; CSP chặn inline script.</t>
+          <t>Given đầu vào chứa ', ", $where, {$ne:null}, .*, ${jndi:...}, Then được xử lý như văn bản thường; không đổi hành vi truy vấn; không lỗi 500.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>TC-SEC-08</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>XSS lưu trữ: script trong lý do khám, bệnh sử, tên, tên tệp</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC15</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>e2e</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>web/e2e/booking.spec.ts::TC-SEC-08 văn bản độc hại trong lý do khám được hiển thị như</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ kiểm ở giao diện với dữ liệu giả; chưa kiểm API/dịch vụ thật.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Given văn bản chứa &lt;script&gt; hoặc onerror=, When hiển thị trên mọi màn hình, Then được mã hóa; không thực thi mã; CSP chặn inline script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-09</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Tiêu đề bảo mật của web: CSP, HSTS, X-Frame-Options, X-Content-Type-Options, Referrer-Policy, không lộ phiên bản máy chủ</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC15</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>nginx-security-headers.conf::Content-Security-Policy
 headers.spec.ts::TC-SEC-09
@@ -9212,59 +9265,6 @@
 web/e2e/headers.spec.ts::TC-SEC-09 cấu hình và trang gốc không được cache; không lộ t</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Given web được phục vụ, When kiểm tra phản hồi, Then đủ các tiêu đề; không có 'unsafe-inline' cho script.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>TC-SEC-10</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Quét bảo mật động (OWASP ZAP baseline) không có lỗi mức High</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC15</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>qa.yml::dast-web</t>
-        </is>
-      </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -9273,135 +9273,135 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Given web chạy trong container, When ZAP baseline quét, Then 0 lỗi FAIL; cảnh báo được ghi vào báo cáo.</t>
+          <t>Given web được phục vụ, When kiểm tra phản hồi, Then đủ các tiêu đề; không có 'unsafe-inline' cho script.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>TC-SEC-10</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Quét bảo mật động (OWASP ZAP baseline) không có lỗi mức High</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC15</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>qa.yml::dast-web</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>viethung12062005</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Given web chạy trong container, When ZAP baseline quét, Then 0 lỗi FAIL; cảnh báo được ghi vào báo cáo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-11</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Không có PII/PHI trong log, metric, trace, sự kiện, URL, thông báo lỗi</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC13, NFR-O4</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>OutboxTest.java::lastErrorNeverContainsThePayload
 AuditTest.java::longReasonIsRejectedAndLongUserAgentTruncated</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Mới kiểm outbox/audit không lộ nội dung; cần quét log, trace, sự kiện của luồng thật (script tools/qa/pii_scan khi có service chạy).</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr">
+      <c r="K165" s="2" t="inlineStr">
         <is>
           <t>Given chạy luồng đặt lịch và hồ sơ với dữ liệu giả có tên, SĐT, email dễ nhận diện, When quét toàn bộ log, sự kiện, trace, Then không tìm thấy các giá trị đó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>TC-SEC-12</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Thông báo lỗi không lộ stack trace, tên bảng, đường dẫn, phiên bản framework</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>NFR-SEC13</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>viethung12062005</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>Given yêu cầu gây lỗi (JSON sai, kiểu sai, ID lạ), Then phản hồi là Problem Details/OperationOutcome chuẩn không chứa chi tiết nội bộ.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-13</t>
+          <t>TC-SEC-12</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Tệp upload: đổi đuôi, tệp lai (polyglot), quá cỡ, tên tệp có ../, tệp EICAR</t>
+          <t>Thông báo lỗi không lộ stack trace, tên bảng, đường dẫn, phiên bản framework</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC17</t>
+          <t>NFR-SEC13</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -9437,24 +9437,24 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Given từng loại tệp độc hại, Then bị từ chối hoặc cách ly; tên đối tượng do hệ thống sinh; không ghi ra ngoài thư mục đích.</t>
+          <t>Given yêu cầu gây lỗi (JSON sai, kiểu sai, ID lạ), Then phản hồi là Problem Details/OperationOutcome chuẩn không chứa chi tiết nội bộ.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-14</t>
+          <t>TC-SEC-13</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Link upload/tải: dùng lại, đổi đường dẫn, dùng sau khi hết hạn, dùng cho tệp khác</t>
+          <t>Tệp upload: đổi đuôi, tệp lai (polyglot), quá cỡ, tên tệp có ../, tệp EICAR</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC17, AC-05.2</t>
+          <t>NFR-SEC17</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -9490,24 +9490,24 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Given link đã cấp, When đổi đối tượng, dùng quá hạn hay dùng khác phương thức, Then bị từ chối.</t>
+          <t>Given từng loại tệp độc hại, Then bị từ chối hoặc cách ly; tên đối tượng do hệ thống sinh; không ghi ra ngoài thư mục đích.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-15</t>
+          <t>TC-SEC-14</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Giới hạn tốc độ và chống dò: khóa tạm sau 5 lần đăng nhập sai, 429 khi vượt, tìm kiếm không liệt kê hàng loạt</t>
+          <t>Link upload/tải: dùng lại, đổi đường dẫn, dùng sau khi hết hạn, dùng cho tệp khác</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC16</t>
+          <t>NFR-SEC17, AC-05.2</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9543,24 +9543,24 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Given 11 yêu cầu đặt lịch/phút, Then yêu cầu thứ 11 nhận 429; Given điều kiện tìm 2 ký tự, Then bị từ chối.</t>
+          <t>Given link đã cấp, When đổi đối tượng, dùng quá hạn hay dùng khác phương thức, Then bị từ chối.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-16</t>
+          <t>TC-SEC-15</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Phản hồi tìm kiếm chỉ có trường tối thiểu (che SĐT, không chẩn đoán, không địa chỉ)</t>
+          <t>Giới hạn tốc độ và chống dò: khóa tạm sau 5 lần đăng nhập sai, 429 khi vượt, tìm kiếm không liệt kê hàng loạt</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC10</t>
+          <t>NFR-SEC16</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -9596,24 +9596,24 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>Given kết quả tìm bệnh nhân, Then chỉ có họ tên, năm sinh, giới, mã, SĐT che 4 số giữa.</t>
+          <t>Given 11 yêu cầu đặt lịch/phút, Then yêu cầu thứ 11 nhận 429; Given điều kiện tìm 2 ký tự, Then bị từ chối.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-17</t>
+          <t>TC-SEC-16</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Prompt injection: câu hỏi và tài liệu chứa chỉ thị độc hại (50 mẫu) không đổi hành vi</t>
+          <t>Phản hồi tìm kiếm chỉ có trường tối thiểu (che SĐT, không chẩn đoán, không địa chỉ)</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>NFR-AI3, NFR-SEC8, AC-11.2</t>
+          <t>NFR-SEC10</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -9649,24 +9649,24 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Given bộ 50 mẫu tấn công trong câu hỏi và trong tài liệu nguồn, Then 0 lần vượt rào; không tiết lộ prompt hệ thống; không gọi công cụ ngoài danh sách.</t>
+          <t>Given kết quả tìm bệnh nhân, Then chỉ có họ tên, năm sinh, giới, mã, SĐT che 4 số giữa.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-18</t>
+          <t>TC-SEC-17</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu gửi nhà cung cấp LLM bên ngoài đã được che định danh</t>
+          <t>Prompt injection: câu hỏi và tài liệu chứa chỉ thị độc hại (50 mẫu) không đổi hành vi</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC8, AC-SM.2</t>
+          <t>NFR-AI3, NFR-SEC8, AC-11.2</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -9702,24 +9702,24 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Given chặn kết nối ra ngoài bằng máy chủ giả, When tóm tắt, trích xuất, hỏi đáp, Then thân yêu cầu không có họ tên, SĐT, email, địa chỉ của dữ liệu giả.</t>
+          <t>Given bộ 50 mẫu tấn công trong câu hỏi và trong tài liệu nguồn, Then 0 lần vượt rào; không tiết lộ prompt hệ thống; không gọi công cụ ngoài danh sách.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-19</t>
+          <t>TC-SEC-18</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>AI chỉ có quyền của người gọi (on-behalf-of): không đọc được dữ liệu ngoài quyền</t>
+          <t>Dữ liệu gửi nhà cung cấp LLM bên ngoài đã được che định danh</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC8, AC-12.1</t>
+          <t>NFR-SEC8, AC-SM.2</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -9755,24 +9755,24 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Given người dùng không có quan hệ điều trị, When gọi tính năng AI với mã bệnh nhân đó, Then bị từ chối; dịch vụ AI không dùng thông tin đăng nhập riêng để đọc.</t>
+          <t>Given chặn kết nối ra ngoài bằng máy chủ giả, When tóm tắt, trích xuất, hỏi đáp, Then thân yêu cầu không có họ tên, SĐT, email, địa chỉ của dữ liệu giả.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-20</t>
+          <t>TC-SEC-19</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Giả mạo giữa các service: gọi endpoint nội bộ /internal từ bên ngoài hoặc từ service không khai báo</t>
+          <t>AI chỉ có quyền của người gọi (on-behalf-of): không đọc được dữ liệu ngoài quyền</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC7, NFR-SEC2</t>
+          <t>NFR-SEC8, AC-12.1</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -9808,24 +9808,24 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Given yêu cầu từ ngoài tới /internal/*, Then gateway chặn; Given service không được khai báo, Then NetworkPolicy và kiểm tra danh tính chặn.</t>
+          <t>Given người dùng không có quan hệ điều trị, When gọi tính năng AI với mã bệnh nhân đó, Then bị từ chối; dịch vụ AI không dùng thông tin đăng nhập riêng để đọc.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-21</t>
+          <t>TC-SEC-20</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Cách ly mạng: kết nối trái phép giữa pod, tới CSDL từ ngoài cụm bị chặn</t>
+          <t>Giả mạo giữa các service: gọi endpoint nội bộ /internal từ bên ngoài hoặc từ service không khai báo</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC7</t>
+          <t>NFR-SEC7, NFR-SEC2</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -9861,24 +9861,24 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Given NetworkPolicy mặc định chặn, When thử kết nối từ pod không được khai báo, Then thất bại.</t>
+          <t>Given yêu cầu từ ngoài tới /internal/*, Then gateway chặn; Given service không được khai báo, Then NetworkPolicy và kiểm tra danh tính chặn.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-22</t>
+          <t>TC-SEC-21</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>TLS: không chấp nhận TLS &lt; 1.2, không có mã hóa yếu, chứng chỉ hợp lệ, kể cả trong cụm</t>
+          <t>Cách ly mạng: kết nối trái phép giữa pod, tới CSDL từ ngoài cụm bị chặn</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC3</t>
+          <t>NFR-SEC7</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -9914,24 +9914,24 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Given quét cấu hình TLS của gateway và các kết nối nội bộ, Then chỉ TLS 1.2+ với bộ mã mạnh.</t>
+          <t>Given NetworkPolicy mặc định chặn, When thử kết nối từ pod không được khai báo, Then thất bại.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-23</t>
+          <t>TC-SEC-22</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Không có secret trong mã nguồn, image, lịch sử git; secret chỉ ở Key Vault</t>
+          <t>TLS: không chấp nhận TLS &lt; 1.2, không có mã hóa yếu, chứng chỉ hợp lệ, kể cả trong cụm</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC4</t>
+          <t>NFR-SEC3</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>security</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -9951,15 +9951,15 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>pr-checks.yml::pr-checks</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
@@ -9967,24 +9967,24 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Given quét gitleaks toàn bộ lịch sử, quét image và cấu hình, Then không có secret.</t>
+          <t>Given quét cấu hình TLS của gateway và các kết nối nội bộ, Then chỉ TLS 1.2+ với bộ mã mạnh.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-24</t>
+          <t>TC-SEC-23</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Chuỗi cung ứng: thư viện, image, workflow đã ghim, quét, ký và có SBOM</t>
+          <t>Không có secret trong mã nguồn, image, lịch sử git; secret chỉ ở Key Vault</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC6</t>
+          <t>NFR-SEC4</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -10004,19 +10004,15 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>automated</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>svc-web.yml::container</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>Chưa kiểm cụm từ chối image không ký.</t>
-        </is>
-      </c>
+          <t>pr-checks.yml::pr-checks</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
@@ -10024,24 +10020,24 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Given pipeline mỗi PR và nightly, Then Trivy, OSV, Dependency-Check, hadolint chạy; image ký cosign; cụm từ chối image không ký.</t>
+          <t>Given quét gitleaks toàn bộ lịch sử, quét image và cấu hình, Then không có secret.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-25</t>
+          <t>TC-SEC-24</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Truy cập khẩn cấp: không vượt phạm vi một bệnh nhân, hết hạn 60 phút, báo DPO, ghi audit mục đích</t>
+          <t>Chuỗi cung ứng: thư viện, image, workflow đã ghim, quét, ký và có SBOM</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>AC-10.1, AC-BG.1, AC-BG.3</t>
+          <t>NFR-SEC6</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -10051,7 +10047,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -10061,13 +10057,17 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>svc-web.yml::container</t>
+        </is>
+      </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
+          <t>Chưa kiểm cụm từ chối image không ký.</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -10077,24 +10077,24 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Given quyền khẩn cấp cho bệnh nhân A, When mở bệnh nhân B hoặc sau 60 phút, Then bị từ chối.</t>
+          <t>Given pipeline mỗi PR và nightly, Then Trivy, OSV, Dependency-Check, hadolint chạy; image ký cosign; cụm từ chối image không ký.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-26</t>
+          <t>TC-SEC-25</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Audit bất biến: không sửa/xóa qua API, giao diện, tài khoản lưu trữ; chuỗi hash phát hiện sửa</t>
+          <t>Truy cập khẩn cấp: không vượt phạm vi một bệnh nhân, hết hạn 60 phút, báo DPO, ghi audit mục đích</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>AC-09.2, NFR-SEC5</t>
+          <t>AC-10.1, AC-BG.1, AC-BG.3</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -10120,34 +10120,34 @@
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Cần audit-verify và Blob WORM (AUD-02, AUD-06, IAC-12).</t>
+          <t>Chờ tính năng hoặc môi trường tương ứng được hiện thực.</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>viethung12062005</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>Given bản ghi audit đã ghi, When cố sửa/xóa bằng mọi đường, Then thất bại; audit-verify phát hiện đứt chuỗi.</t>
+          <t>Given quyền khẩn cấp cho bệnh nhân A, When mở bệnh nhân B hoặc sau 60 phút, Then bị từ chối.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-27</t>
+          <t>TC-SEC-26</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Thiết bị dùng chung: đăng xuất xóa dữ liệu bệnh nhân khỏi bộ nhớ, nút Back không hiện lại</t>
+          <t>Audit bất biến: không sửa/xóa qua API, giao diện, tài khoản lưu trữ; chuỗi hash phát hiện sửa</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>NFR-SEC14</t>
+          <t>AC-09.2, NFR-SEC5</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -10173,80 +10173,133 @@
       <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Giao diện chưa có đăng xuất xóa dữ liệu và chặn Back (WEB-xx).</t>
+          <t>Cần audit-verify và Blob WORM (AUD-02, AUD-06, IAC-12).</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Given đã xem hồ sơ rồi đăng xuất, When bấm Back, Then không hiển thị dữ liệu; sessionStorage/localStorage không còn token hay dữ liệu bệnh nhân.</t>
+          <t>Given bản ghi audit đã ghi, When cố sửa/xóa bằng mọi đường, Then thất bại; audit-verify phát hiện đứt chuỗi.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
+          <t>TC-SEC-27</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Thiết bị dùng chung: đăng xuất xóa dữ liệu bệnh nhân khỏi bộ nhớ, nút Back không hiện lại</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>NFR-SEC14</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>e2e</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Giao diện chưa có đăng xuất xóa dữ liệu và chặn Back (WEB-xx).</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Given đã xem hồ sơ rồi đăng xuất, When bấm Back, Then không hiển thị dữ liệu; sessionStorage/localStorage không còn token hay dữ liệu bệnh nhân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
           <t>TC-SEC-28</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Không lưu token trong localStorage; hết phiên theo thời gian không thao tác</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>NFR-SEC14, NFR-SEC1</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>e2e</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>web/e2e/booking.spec.ts::TC-SEC-28 token không nằm trong localStorage</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Chỉ kiểm ở giao diện với dữ liệu giả; chưa kiểm API/dịch vụ thật.</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>viethung12062005</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr">
+      <c r="K182" s="2" t="inlineStr">
         <is>
           <t>Given đăng nhập, Then localStorage không có token; Given 15 phút không thao tác (nhân viên), Then tự đăng xuất.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K181"/>
-  <conditionalFormatting sqref="G2:G181">
+  <autoFilter ref="A1:K182"/>
+  <conditionalFormatting sqref="G2:G182">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"automated"</formula>
     </cfRule>
@@ -10270,7 +10323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12524,12 +12577,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>AC-RS.1</t>
+          <t>AC-RG.2</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-RS.1</t>
+          <t>TC-AC-RG.2</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -12551,12 +12604,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>AC-RS.2</t>
+          <t>AC-RS.1</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-RS.2</t>
+          <t>TC-AC-RS.1</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -12566,7 +12619,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -12578,22 +12631,22 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>AC-SM.1</t>
+          <t>AC-RS.2</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-SM.1</t>
+          <t>TC-AC-RS.2</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -12605,12 +12658,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>AC-SM.2</t>
+          <t>AC-SM.1</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-SM.2</t>
+          <t>TC-AC-SM.1</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -12637,12 +12690,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-18</t>
+          <t>TC-AC-SM.2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -12659,12 +12712,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>AC-SN.1</t>
+          <t>AC-SM.2</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-SN.1</t>
+          <t>TC-SEC-18</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -12674,7 +12727,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -12686,22 +12739,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>AC-SP.1</t>
+          <t>AC-SN.1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-SP.1</t>
+          <t>TC-AC-SN.1</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -12713,44 +12766,44 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>AC-SR.1</t>
+          <t>AC-SP.1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-SR.1</t>
+          <t>TC-AC-SP.1</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>AC-ST.1</t>
+          <t>AC-SR.1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-ST.1</t>
+          <t>TC-AC-SR.1</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -12760,19 +12813,19 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>AC-TL.1</t>
+          <t>AC-ST.1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-TL.1</t>
+          <t>TC-AC-ST.1</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -12782,7 +12835,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -12794,12 +12847,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>AC-TL.2</t>
+          <t>AC-TL.1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-TL.2</t>
+          <t>TC-AC-TL.1</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -12821,12 +12874,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>AC-UD.1</t>
+          <t>AC-TL.2</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-UD.1</t>
+          <t>TC-AC-TL.2</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -12848,17 +12901,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>AC-UD.2</t>
+          <t>AC-UD.1</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-UD.2</t>
+          <t>TC-AC-UD.1</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -12875,17 +12928,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>AC-UP.1</t>
+          <t>AC-UD.2</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-UP.1</t>
+          <t>TC-AC-UD.2</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -12902,12 +12955,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>AC-VD.1</t>
+          <t>AC-UP.1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-VD.1</t>
+          <t>TC-AC-UP.1</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -12929,12 +12982,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>AC-VT.1</t>
+          <t>AC-VD.1</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-VT.1</t>
+          <t>TC-AC-VD.1</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -12956,12 +13009,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>AC-VT.2</t>
+          <t>AC-VT.1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-VT.2</t>
+          <t>TC-AC-VT.1</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -12983,44 +13036,44 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>NFR-A1</t>
+          <t>AC-VT.2</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A1</t>
+          <t>TC-AC-VT.2</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>NFR-A2</t>
+          <t>NFR-A1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A2</t>
+          <t>TC-NFR-A1</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -13030,19 +13083,19 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>NFR-A3</t>
+          <t>NFR-A2</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A3</t>
+          <t>TC-NFR-A2</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -13064,12 +13117,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>NFR-A4</t>
+          <t>NFR-A3</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A4</t>
+          <t>TC-NFR-A3</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -13079,7 +13132,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -13091,12 +13144,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>NFR-A5</t>
+          <t>NFR-A4</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A5</t>
+          <t>TC-NFR-A4</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -13118,12 +13171,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>NFR-A6</t>
+          <t>NFR-A5</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A6</t>
+          <t>TC-NFR-A5</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -13133,7 +13186,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -13145,17 +13198,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>NFR-A7</t>
+          <t>NFR-A6</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-A7</t>
+          <t>TC-NFR-A6</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -13172,17 +13225,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI1</t>
+          <t>NFR-A7</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI1</t>
+          <t>TC-NFR-A7</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -13199,12 +13252,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI2</t>
+          <t>NFR-AI1</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI2</t>
+          <t>TC-NFR-AI1</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -13226,12 +13279,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI3</t>
+          <t>NFR-AI2</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI3</t>
+          <t>TC-NFR-AI2</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -13258,7 +13311,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-17</t>
+          <t>TC-NFR-AI3</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -13268,7 +13321,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -13280,12 +13333,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI4</t>
+          <t>NFR-AI3</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI4</t>
+          <t>TC-SEC-17</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -13295,7 +13348,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -13307,12 +13360,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI5</t>
+          <t>NFR-AI4</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI5</t>
+          <t>TC-NFR-AI4</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -13334,12 +13387,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI6</t>
+          <t>NFR-AI5</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI6</t>
+          <t>TC-NFR-AI5</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -13361,12 +13414,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>NFR-AI7</t>
+          <t>NFR-AI6</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-AI7</t>
+          <t>TC-NFR-AI6</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -13388,17 +13441,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>NFR-C1</t>
+          <t>NFR-AI7</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-C1</t>
+          <t>TC-NFR-AI7</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -13408,24 +13461,24 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>NFR-C2</t>
+          <t>NFR-C1</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-C2</t>
+          <t>TC-NFR-C1</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>review</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -13442,17 +13495,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>NFR-C3</t>
+          <t>NFR-C2</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-C3</t>
+          <t>TC-NFR-C2</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -13469,17 +13522,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NFR-D1</t>
+          <t>NFR-C3</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-D1</t>
+          <t>TC-NFR-C3</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>review</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -13489,24 +13542,24 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NFR-D2</t>
+          <t>NFR-D1</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-D2</t>
+          <t>TC-NFR-D1</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -13523,12 +13576,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NFR-D3</t>
+          <t>NFR-D2</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-D3</t>
+          <t>TC-NFR-D2</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -13550,17 +13603,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NFR-D4</t>
+          <t>NFR-D3</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-D4</t>
+          <t>TC-NFR-D3</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -13570,24 +13623,24 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>NFR-I1</t>
+          <t>NFR-D4</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-I1</t>
+          <t>TC-NFR-D4</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>contract</t>
+          <t>review</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -13597,24 +13650,24 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>NFR-I2</t>
+          <t>NFR-I1</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-I2</t>
+          <t>TC-NFR-I1</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -13624,24 +13677,24 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>NFR-I3</t>
+          <t>NFR-I2</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-I3</t>
+          <t>TC-NFR-I2</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -13658,17 +13711,17 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>NFR-O1</t>
+          <t>NFR-I3</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-O1</t>
+          <t>TC-NFR-I3</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -13678,24 +13731,24 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>NFR-O2</t>
+          <t>NFR-O1</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-O2</t>
+          <t>TC-NFR-O1</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -13705,24 +13758,24 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>NFR-O3</t>
+          <t>NFR-O2</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-O3</t>
+          <t>TC-NFR-O2</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>resilience</t>
+          <t>review</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -13732,24 +13785,24 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>NFR-O4</t>
+          <t>NFR-O3</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-O4</t>
+          <t>TC-NFR-O3</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>resilience</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -13759,7 +13812,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13824,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-11</t>
+          <t>TC-NFR-O4</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -13781,7 +13834,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -13793,22 +13846,22 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>NFR-P1</t>
+          <t>NFR-O4</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P1</t>
+          <t>TC-SEC-11</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -13820,12 +13873,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>NFR-P2</t>
+          <t>NFR-P1</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P2</t>
+          <t>TC-NFR-P1</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -13847,12 +13900,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>NFR-P3</t>
+          <t>NFR-P2</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P3</t>
+          <t>TC-NFR-P2</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -13867,19 +13920,19 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>NFR-P4</t>
+          <t>NFR-P3</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P4</t>
+          <t>TC-NFR-P3</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -13901,17 +13954,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>NFR-P5</t>
+          <t>NFR-P4</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P5</t>
+          <t>TC-NFR-P4</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -13928,12 +13981,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>NFR-P6</t>
+          <t>NFR-P5</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P6</t>
+          <t>TC-NFR-P5</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -13955,17 +14008,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>NFR-P7</t>
+          <t>NFR-P6</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P7</t>
+          <t>TC-NFR-P6</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -13982,17 +14035,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>NFR-P8</t>
+          <t>NFR-P7</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-P8</t>
+          <t>TC-NFR-P7</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -14009,17 +14062,17 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>NFR-S1</t>
+          <t>NFR-P8</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-S1</t>
+          <t>TC-NFR-P8</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -14036,12 +14089,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>NFR-S2</t>
+          <t>NFR-S1</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-S2</t>
+          <t>TC-NFR-S1</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -14056,19 +14109,19 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>NFR-S3</t>
+          <t>NFR-S2</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-S3</t>
+          <t>TC-NFR-S2</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -14090,12 +14143,12 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>NFR-S4</t>
+          <t>NFR-S3</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-S4</t>
+          <t>TC-NFR-S3</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -14110,34 +14163,34 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC1</t>
+          <t>NFR-S4</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC1</t>
+          <t>TC-NFR-S4</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -14149,12 +14202,12 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-04</t>
+          <t>TC-NFR-SEC1</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -14176,12 +14229,12 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-05</t>
+          <t>TC-SEC-04</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -14191,7 +14244,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14203,12 +14256,12 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-06</t>
+          <t>TC-SEC-05</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -14218,7 +14271,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14283,12 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-28</t>
+          <t>TC-SEC-06</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -14245,24 +14298,24 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC10</t>
+          <t>NFR-SEC1</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC10</t>
+          <t>TC-SEC-28</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -14272,7 +14325,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14337,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-NFR-SEC10</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -14311,7 +14364,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-16</t>
+          <t>TC-SEC-03</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -14333,12 +14386,12 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC11</t>
+          <t>NFR-SEC10</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC11</t>
+          <t>TC-SEC-16</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -14360,17 +14413,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC12</t>
+          <t>NFR-SEC11</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC12</t>
+          <t>TC-NFR-SEC11</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -14387,17 +14440,17 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC13</t>
+          <t>NFR-SEC12</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC13</t>
+          <t>TC-NFR-SEC12</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -14419,12 +14472,12 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-NFR-SEC13</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -14446,12 +14499,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-11</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -14461,7 +14514,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14526,12 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-12</t>
+          <t>TC-SEC-11</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -14488,24 +14541,24 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC14</t>
+          <t>NFR-SEC13</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC14</t>
+          <t>TC-SEC-12</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -14527,7 +14580,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-27</t>
+          <t>TC-NFR-SEC14</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -14554,7 +14607,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-28</t>
+          <t>TC-SEC-27</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -14569,24 +14622,24 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC15</t>
+          <t>NFR-SEC14</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC15</t>
+          <t>TC-SEC-28</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -14596,7 +14649,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14608,12 +14661,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-08</t>
+          <t>TC-NFR-SEC15</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -14623,7 +14676,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14688,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-09</t>
+          <t>TC-SEC-08</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -14650,7 +14703,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14715,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-10</t>
+          <t>TC-SEC-09</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -14684,17 +14737,17 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC16</t>
+          <t>NFR-SEC15</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC16</t>
+          <t>TC-SEC-10</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -14704,7 +14757,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14769,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-15</t>
+          <t>TC-NFR-SEC16</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -14738,17 +14791,17 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC17</t>
+          <t>NFR-SEC16</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC17</t>
+          <t>TC-SEC-15</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -14770,7 +14823,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-13</t>
+          <t>TC-NFR-SEC17</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -14797,7 +14850,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-14</t>
+          <t>TC-SEC-13</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -14819,17 +14872,17 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC18</t>
+          <t>NFR-SEC17</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC18</t>
+          <t>TC-SEC-14</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -14846,17 +14899,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC19</t>
+          <t>NFR-SEC18</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC19</t>
+          <t>TC-NFR-SEC18</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -14873,17 +14926,17 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC2</t>
+          <t>NFR-SEC19</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC2</t>
+          <t>TC-NFR-SEC19</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -14893,7 +14946,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -14905,12 +14958,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-NFR-SEC2</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -14920,7 +14973,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14985,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-02</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -14947,7 +15000,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -14959,7 +15012,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-SEC-02</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -14974,7 +15027,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -14986,7 +15039,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-05</t>
+          <t>TC-SEC-03</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -15013,7 +15066,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-07</t>
+          <t>TC-SEC-05</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -15040,12 +15093,12 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-20</t>
+          <t>TC-SEC-07</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -15062,17 +15115,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC20</t>
+          <t>NFR-SEC2</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC20</t>
+          <t>TC-SEC-20</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -15089,17 +15142,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC21</t>
+          <t>NFR-SEC20</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC21</t>
+          <t>TC-NFR-SEC20</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -15109,24 +15162,24 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC3</t>
+          <t>NFR-SEC21</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC3</t>
+          <t>TC-NFR-SEC21</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>review</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -15136,7 +15189,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15201,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-22</t>
+          <t>TC-NFR-SEC3</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -15170,12 +15223,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC4</t>
+          <t>NFR-SEC3</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC4</t>
+          <t>TC-SEC-22</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -15190,7 +15243,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -15202,12 +15255,12 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-23</t>
+          <t>TC-NFR-SEC4</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -15224,17 +15277,17 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC5</t>
+          <t>NFR-SEC4</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC5</t>
+          <t>TC-SEC-23</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -15244,7 +15297,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15309,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-26</t>
+          <t>TC-NFR-SEC5</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -15271,24 +15324,24 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC6</t>
+          <t>NFR-SEC5</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC6</t>
+          <t>TC-SEC-26</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>ci</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -15298,7 +15351,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15363,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-24</t>
+          <t>TC-NFR-SEC6</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -15332,17 +15385,17 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC7</t>
+          <t>NFR-SEC6</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC7</t>
+          <t>TC-SEC-24</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -15352,7 +15405,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>partial</t>
         </is>
       </c>
     </row>
@@ -15364,12 +15417,12 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-20</t>
+          <t>TC-NFR-SEC7</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -15391,12 +15444,12 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-21</t>
+          <t>TC-SEC-20</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -15413,17 +15466,17 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC8</t>
+          <t>NFR-SEC7</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC8</t>
+          <t>TC-SEC-21</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>ai-eval</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -15445,7 +15498,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-17</t>
+          <t>TC-NFR-SEC8</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -15472,12 +15525,12 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-18</t>
+          <t>TC-SEC-17</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>ai-eval</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -15499,7 +15552,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>TC-SEC-19</t>
+          <t>TC-SEC-18</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -15521,17 +15574,17 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>NFR-SEC9</t>
+          <t>NFR-SEC8</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>TC-NFR-SEC9</t>
+          <t>TC-SEC-19</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -15541,39 +15594,66 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>planned</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
+          <t>NFR-SEC9</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>TC-NFR-SEC9</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
           <t>NFR-U1</t>
         </is>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>TC-NFR-U1</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>e2e</t>
         </is>
       </c>
-      <c r="D196" s="3" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E196" s="3" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E196"/>
+  <autoFilter ref="A1:E197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
